--- a/exemplos/cronograma-exemplo-aiarq.xlsx
+++ b/exemplos/cronograma-exemplo-aiarq.xlsx
@@ -942,11 +942,11 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
@@ -958,11 +958,9 @@
       </c>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>0.21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
     </row>
